--- a/Excel/11_Wastewater_WIP_v02.prename.bak.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F84FDF4-8C41-443A-B5C4-709AB3E97C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BC3BEA-54C2-4A1C-B350-56320BDBAC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="11.1.1-2 Wastewater CH4" sheetId="69" r:id="rId5"/>
     <sheet name="11.1.3-4 Wastewater N2O" sheetId="120" r:id="rId6"/>
     <sheet name="Constants - Wastewater" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="124" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="125" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -178,6 +181,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -1947,176 +1951,6 @@
   <dxfs count="71">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2976,6 +2810,176 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5237,6 +5241,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5320,7 +5344,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{AFAB6A22-121F-4A50-9152-A8E580122815}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{60FD3DEC-6132-42B3-A699-403587965D5D}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5328,16 +5352,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F2A7B006-3B9B-490B-A956-7F904A9BC1A0}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{BA6726C5-D9D8-4D31-81EC-1DC25061E31A}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A3178854-1904-46B6-9601-FBCC390F839C}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{3048A7D2-7F93-4BD0-9D8D-67272EA18191}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D21F920E-74C3-43C6-8E18-6CFD69944EC3}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{92686BF3-D26B-4679-A40A-852EA84EF852}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{39CF9EA2-C9B6-41EC-AC58-E1943DCC6E03}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{80BA2E2F-6FE0-47D7-9D6D-BFE5E2A9803C}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5346,16 +5370,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{DB5808CD-4C52-49C0-8D9C-DDD27E7ABF86}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{44509B1C-FA74-4B9E-8E16-B7B10FA0ECC6}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4B17C9DE-741E-4223-8B98-9DA237A2543C}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{13EB0E21-1496-43EC-A6FE-FD07ED44F742}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9AE87DF0-C92B-4748-9688-790D35C88B2F}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{8AAA12F3-3158-4160-9D90-F1610DF90862}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5364,16 +5388,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{F67892C5-921B-4BA8-8C3E-941A4EBD5456}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{09B1D7CC-650C-4C00-B0D6-0FD99E350EB9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F1C79171-18D4-4538-B8B5-4035B9BDADE4}" name="Data source">
+    <tableColumn id="1" xr3:uid="{F52A7569-0DA7-402F-9AB1-034B445EB227}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F4879EF9-AFF2-4FBB-8AC4-10E9136CB398}" name="Data score">
+    <tableColumn id="2" xr3:uid="{5FD42A51-4C3A-4D1E-A42B-5DA4BF5DCFE0}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5382,16 +5406,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{B1B8ACAC-A09F-4E48-8944-728EA0065A24}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{DB760DD5-0237-49A8-A230-B47BB1156DE6}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AC686EA2-8D9A-4D6D-A8A8-062FB3B515CC}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{8881F848-5C9D-4A93-8F3E-9FE78E12D9D8}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1FCEBDA5-65F4-46B1-B370-C11FB49932FA}" name="FracWET" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{52CFFC82-08BD-4302-B2DD-3522C2AD5970}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5400,7 +5424,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{90C0F7AC-0F98-4652-98CC-95BA4A16C131}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{A7E72203-13BC-4CF7-8169-9096D04EF218}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5409,19 +5433,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DC10BB70-498C-4145-BAE7-7A04D5280125}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{F8821A07-CBB8-4D58-99FC-46F9AD9B5D06}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9A35A152-BB7C-4846-9F6E-3E9C99E73442}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{808B110B-F4D1-4235-BBE7-A5087AB78BB7}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{748EC603-7F46-49E5-A98E-535FE8846206}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{40B5F840-D9A5-424C-83F4-4BDB382EFDB0}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A56CD644-C6AA-445E-9F25-4B23A92A9B64}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{4958BC5B-064E-4A15-857F-352B01797ABD}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CCAB1984-3AF3-43D3-81A5-8CE900C98160}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{A5274952-A1AF-48A5-B96E-D6095F4217A2}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5430,16 +5454,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{4165A077-B250-4DEE-B369-59E4E7679902}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{1603577B-1419-4AE9-B52C-CD309767E134}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F2C9E476-6A55-47D9-B3E7-C67EA63535FA}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{20911576-3EF0-4E1B-A889-87C3CAF4193A}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{88DAA629-0590-41E1-A2CC-610CF9FDB97C}" name="FracWET" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A8928862-0C55-4701-8E46-0460079190AF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5448,16 +5472,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{87CE216A-9BD9-485A-9EB8-B9E0DFCC2C93}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{DC5AB438-CBE2-4FFD-BDA9-A83CADD87D88}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AF9CBDC1-27EF-4EED-B8DF-92F594F394C9}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{D234EE0E-8F92-4312-BE63-502F946046A1}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F1AF672B-1B1A-422D-A6B3-621D6214B60E}" name="EFPRP" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{7E21E7A6-BB56-4CBA-A22A-56D6354C8C0E}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5466,16 +5490,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{DEDBE9B8-7638-405B-BBEA-28F4A90E5FDC}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{D3C26136-7D0C-4262-9DD3-BEB3843BEDE5}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F56D4BDC-1A8D-48FE-B31E-DE67F81E1C52}" name="Month">
+    <tableColumn id="1" xr3:uid="{4CBF8390-5415-4AD3-9812-F085B12FA77F}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{84A8C1F6-0D04-4FAE-AC8C-5DCE94CD2667}" name="Season" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{12C3240D-243B-47E8-86C5-1020AD6AFF31}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5484,7 +5508,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{FB2C0D77-D19C-4F62-8E5B-44E9019BF690}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{81F10B7B-DBB5-42D3-8E22-E1B4096BF026}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5504,52 +5528,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F0787CE1-8BC3-48A0-BD72-4D31FF2981AB}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{D9579F68-9384-4395-9B40-A666F880BDDB}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{236F7AC5-AA7A-4B5B-A91D-B3234A850B1F}" name="MAT (ºC)" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B5C3A31B-2242-46CB-B0BD-99DE0082E553}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C188DBCE-83A9-4948-B739-6D8CFA8FB1F1}" name="Anaerobic lagoon" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{B4374E36-14BC-476E-901E-FAF15F4C4C67}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7F0A7CCE-9091-445B-A615-A547A51F5200}" name="Digester / covered lagoons" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{6EFD5B4A-1034-4FCF-8049-14B5F75E9A5F}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F45FD72F-73B7-4580-B927-C93DC98F52E5}" name="Liquid systems" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{2F2DF928-E0E4-4BDB-8FF2-39BADE8602B4}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C72DB022-C4D0-41C7-A672-C4F576EDC815}" name="Daily spread" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{A408F48C-E01F-4C66-B671-371CEDB14FA8}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{98BE1154-A30B-4B37-8D42-1FCB8196ADFF}" name="Composting (passive windrow)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{EA17D570-9828-4407-9280-37420A993AAB}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FE6F67A9-BD27-47E8-B501-A2D2DDFAFD2B}" name="Solid storage" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{8F2C9E0D-DA9D-429C-82B7-E2683EF71F6F}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1612D188-6F19-4A62-9F7B-984763732FCD}" name="Pit storage" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{08E56A3F-15A4-4F37-BAE2-6B57DDFE2992}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F2B629FE-D9AC-43BB-8712-0244FAFED160}" name="Deep litter" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{A3C2F1A6-E172-41C6-8C78-5E47C0C5C747}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AEB1AAB3-C1F7-4609-811C-C8F71F27BEA7}" name="Poultry manure with bedding" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{6F45BD40-E4D6-4DCC-87FC-414A1FBEFEA6}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{30CD3C79-0D8E-4E7F-87FD-8F4EA6115707}" name="Poultry manure without bedding" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{17DA757C-6CDA-4C52-B8B6-420D5941EF6C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B6966C78-6D1B-4D36-AF62-930896F91722}" name="Direct processing" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{5268FDA8-7DF2-4A8C-AACF-EF2AB5BC2B49}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{319A832A-BD0E-4DCC-BA3B-3FE865BD158B}" name="Direct application" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{B004BF9B-155B-4440-A60F-7DFCC41D53AD}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1A0A5924-316D-4A5B-BC7C-60065B83EB70}" name="Pasture range and paddock" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{8ABF53AC-2C64-414A-977B-8E8C687200DB}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{41772124-674F-460B-8395-C3AE2FD9C178}" name="MAT raw" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{165C0C41-E29C-484F-9F19-554BFA51EA9B}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5558,16 +5582,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{79E744CC-76BA-4DD4-AC67-44F809197B90}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{782546F2-95EA-4798-BEF5-E9A9FD9348A7}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9399ABC9-646D-4864-8875-225CB798A120}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{AA931D7D-C70B-44B6-A950-2C74FE01DBD7}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{828CCD4A-4F4D-4667-8FE5-C00753040270}" name="EFNi &amp; EFN2Oi" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B414394C-46C8-4708-A016-96AB55B2CB24}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5594,20 +5618,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BAB9D8D8-A94C-4765-A2F4-FBF3EB858A25}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2901E4-74D4-491C-9839-A10E08538903}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{171512E4-DD77-45F5-A7DC-7F756E38E58B}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{13A7A6A1-7645-4FB3-95BA-39FF4C7FE645}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{67A2E349-9D96-4192-BF1C-973FE556FADB}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{417988F4-ED4B-45FF-A91E-9D85E753F6E4}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6C9B778A-6BC0-4CBC-92FC-621305E6382A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{B962FF60-EEFE-4021-AD77-4E3462E1AF13}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5616,12 +5640,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D149E782-62CC-4024-A8A1-E5EA1E498D2A}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2813C8E6-E9CE-4977-8FB4-47FB574DC02B}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9D56D53A-6694-4B57-A02F-8E9551CB7A14}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{ABC00590-0BDD-4727-A087-CF9BFD527FC6}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5630,16 +5654,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{BDA15D44-60E0-4864-879A-DD3FCF3315EE}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE88C359-14EF-4A97-A2E4-175687F0066C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{29D0E979-289C-49F4-93D3-6124A7F51BE5}" name="Gas">
+    <tableColumn id="1" xr3:uid="{E9620700-E2AA-43F7-823B-1D93E54A99A9}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F1769B4A-4D35-4F1E-B9DA-F65441424CD9}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{9A583022-0F51-47E6-9CF0-DCE0148B9061}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5648,7 +5672,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{F352728F-1C63-4F70-B975-4EF1CA2C819D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8E394016-4C3B-4484-A0FF-3CFB83C5E43D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5657,19 +5681,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4AD24F5B-C1DA-4F22-BB17-81A6F8D71410}" name="Gas">
+    <tableColumn id="1" xr3:uid="{D7EC98A6-A45F-4EEE-9F93-E4FB3D0A7D7D}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B50E9557-5672-4944-AC8B-E65E187DE052}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{73EF9163-4C06-47F3-8994-067EFD7F0FE5}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{85EF82D1-0A91-4FC0-96CC-52E8DE88242E}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{DE75DEEB-09D7-4CFF-885C-AF9F1D49BD34}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{CC9DBC6F-DAFE-493B-A2AD-0B39C1BB80DB}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{213C32CE-1368-48BB-87AB-0D2F801910D0}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B37F38D1-8FCD-4B3A-A678-FA02F0A28A61}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{FF28DF7C-D3F6-4240-9ED5-975D79231313}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5678,7 +5702,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{0570EA12-3286-4560-9BE6-60258611BC9D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{2678E15E-9743-4D6B-B08F-54FA1F7BD4E6}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5698,52 +5722,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{6ED0CF1D-7CD9-4066-8EE4-25FE923E5D3B}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{258A2775-12F7-4B6E-B50C-2B734CED6764}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CF963462-2F2C-4BF6-A892-086541529F20}" name="MAT" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{CA57A8D6-0E1B-4395-8BBD-8EB2909C6375}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1B3F3876-9D6F-447A-A423-66E21AC0558A}" name="MAP" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{640685BD-3D0B-4B49-994F-2049CD844190}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A4802F3E-DC20-40F1-AC5A-D182C68519BB}" name="Frost days per year" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{B41BB388-73CC-4E31-9702-0644757B771D}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1F7F9556-3126-439E-875C-D76E463F8036}" name="Elevation" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{F65571A7-99C4-419A-ACC9-DB99F6270790}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DBB23AF3-C817-42CE-BE89-ADDA8D904773}" name="MAP:PET" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{1A2EB41B-4703-47CB-A6BA-B23ECFDE75DC}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{60216B5C-783A-4916-AACF-4280FF3BECAD}" name="Min temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{D4FCC700-6BCB-42F6-A269-73CB179D12DE}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1FE05885-DAC3-47B8-BEB3-6920E3033122}" name="Max temp" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{0B04A76E-8B93-43EF-9F74-AAE65AEC4441}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{2B644226-778B-401E-99C4-CEB1DE3EDAE1}" name="Min rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{13D3D99C-422D-4DB4-BAFE-4D5F232E4C8B}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B73B8CF5-08DF-4843-B82E-B9FB1813470C}" name="Max rainfall" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{23F7ECD7-4755-4ED3-8B32-64F398DDA30D}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2516891E-4C4A-426D-8B84-5149409BFCBC}" name="Min frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{358C427E-C96B-4053-A990-1B2058EBFC64}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{189C1E5A-6304-4676-A9EB-8B293F4544B2}" name="Max frost days" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{3130F307-B98C-4067-B80F-2542F94A1BE0}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{14B9E9DB-0BCC-48C2-8CCA-57C75DB45D61}" name="Min elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{8D192874-9822-4C4F-9A9E-B334BAC2FFB8}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{67D82299-FF27-4038-A32D-781A02A531ED}" name="Max elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{A79D36E5-993C-4167-BDE8-6407717CAB24}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FB2C0315-064C-437A-86D7-3E8FA9F4822B}" name="Min MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{A4876D80-2BA9-4B93-A438-B39231AC151A}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{378C37E5-D887-4B5C-9001-232EF0A792B4}" name="Max MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{C13F21D8-24C0-4A6E-8DE5-7781BD4EA367}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5752,16 +5776,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{4D2F7A40-370B-4A1A-BB7E-6930F4763E13}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{ABD9088D-21E6-4B13-B698-A88D317D61B7}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{44AAB7B6-31A0-4522-84AE-3428F2D4D02F}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{42339138-CF75-47CE-98E2-00C999CD6CD9}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8619F0C7-D005-4F89-B453-E75937AA076E}" name="Wet or Dry Zone" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{53AA9C04-0F8D-43AC-AB39-360AF88BE8CC}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5770,7 +5794,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{DA18547E-C2B9-4253-9B23-ECFAF5D3F0C4}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F0282294-800C-4FCE-87FB-E5433DFD7DD5}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5778,16 +5802,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{05952A61-6A28-4826-9977-99686E3CA96D}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{EB6FF107-1CC5-47A6-BFC2-A373ED5BA9DC}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F49ABE84-00CE-4251-9431-9E6E70A546AC}" name="MAT">
+    <tableColumn id="2" xr3:uid="{81FB7AAB-B954-4F7F-880E-D1D6DDF943A7}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0323FC01-6733-41DC-9E79-98C1FED01EC8}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{F72C74A5-51F2-4215-9ABA-7C66657A62EE}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F9992E54-F3A7-462B-BC56-E5BA0C72765F}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{6AA30C8F-73A6-4FD1-B809-BD18E5A99F76}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7818,87 +7842,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D39:H43">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F148:F149">
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F160:F161">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F172:F173">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="12" priority="94" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="94" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F265:F266">
-    <cfRule type="cellIs" dxfId="11" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F270:F271">
-    <cfRule type="cellIs" dxfId="10" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="9" priority="86" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="86" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F299:F300">
-    <cfRule type="cellIs" dxfId="8" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F304:F305">
-    <cfRule type="cellIs" dxfId="7" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I65:I69">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I73 I132">
-    <cfRule type="cellIs" dxfId="5" priority="75" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="75" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I84:I86">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I90:I93">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I97:I101">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8 I51:I52 H53:H55 I54 I56:I58 I60:I61 I212 I218 E220:G220">
-    <cfRule type="cellIs" dxfId="1" priority="80" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="80" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J37 I45 F136:F137">
-    <cfRule type="cellIs" dxfId="0" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="22" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9766,7 +9790,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB47BE6-A391-432F-B8D2-A68CD0E0E20E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9990F8D9-C280-49C7-B33D-9DB18A15652B}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13758,6 +13782,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -13768,16 +13801,11 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAOgAgAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAcwBsAHUAZABnAGUALAB0ACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4ANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgB3AHcAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAIAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBGAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGsAZwAgAEMATwBEAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAyADUAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAQwBmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcASgAgAC8AIABtADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAwADMANwA3ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAEMASAA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAEcASgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAyADgAOQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAE4AMgBPAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABOADIATwAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAxAC4AMQAzADIAZQAtADQAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxADoAIABXAGEAcwB0AGUAdwBhAHQAZQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxAC4AMwAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AbgBzAGkAdABlACAAVwBhAHMAdABlAHcAYQB0AGUAcgAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABuAFEAXwBmAGwAYQByAGUAZAAgAD0AIAB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAG8AcgAgAEcASgApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwAgACgAawBnACAATgAyAE8ALwBHAEoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBmAGwAYQByAGUAZAAsACAARQBDAF8AZgBsAGEAcgBlAGQALAAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACwAXABuACAAIAAgACAAKABRAF8AZgBsAGEAcgBlAGQAIAAvACAAMQAwADAAMAApACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADMALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwBFAEMAXwB7AGYAbABhAHIAZQBkAH0AIABcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABcAHIAaQBnAGgAdABdAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIARwBKAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -13972,11 +14000,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEAOgAgAFcAYQBzAHQAZQB3AGEAdABlAHIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMQAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwBuAHMAaQB0AGUAIABXAGEAcwB0AGUAdwBhAHQAZQByACAATQBhAG4AYQBnAGUAbQBlAG4AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAbgBFAF8AQwBIADQAXABuAHQAIABDAEgANABcAG4ARQBfAHsAQwBIADQAfQA9AFwAXABmAHIAYQBjAHsAMQB9AHsAMQAwADAAMAB9AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBcAFwAbABlAGYAdAAoAFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAKABDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBzAGwAdQBkAGcAZQB9ACkALQBDAE8ARABfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAdwB3ACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHcAdwB9AFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgARgBfAHsAcwBsAHUAZABnAGUAfQAtAEYAXwB7AHIAZQBtAG8AdgBlAGQAfQApAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewBzAGwAdQBkAGcAZQAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBzAGwAdQBkAGcAZQB9AFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0ACgANgAuADcAOAA0AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0ANAB9AFwAXAB0AGkAbQBlAHMAKABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AKQBcAFwAcgBpAGcAaAB0ACkAKwBcAFwAbABlAGYAdAAoAFEAXwB7AGYAbABhAHIAZQBkAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAG4AVwBfAHQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgACgAbQAzACkAXABuAEMATwBEAF8AaQBuACAAPQAgAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABDAE8ARAAgAHIAZQBtAG8AdgBlAGQAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAGEAcwAgAHMAbAB1AGQAZwBlAFwAbgBDAE8ARABfAG8AdQB0ACAAPQAgAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGsAZwAgAEMATwBEAC8AbQAzACkAXABuAEMARgBfAHcAdwBfAHQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcAG4ARQBGAF8AdwB3ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAEYAXwByAGUAbQBvAHYAZQBkACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXABuAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIABzAGwAdQBkAGcAZQBcAG4ARQBGAF8AcwBsAHUAZABnAGUAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgACgAawBnACAAQwBPADIAZQAvAGsAZwAgAEMATwBEACkAXABuAFEAXwBjAGEAcAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAGYAbABhAHIAZQBkACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAEMASAA0ACkAXABuAFEAXwBvAHUAdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgACgAbQAzACAAQwBIADQAKQBcAG4ARQBDAF8AZgBsAGEAcgBlAGQAIAA9ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABHAEoALwBtADMAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBDAEgANAAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAawBnACAAQwBPADIAZQAvAEcASgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwB0ACwAIABDAE8ARABfAGkAbgAsACAARgBfAHMAbAB1AGQAZwBlACwAIABDAE8ARABfAG8AdQB0ACwAIABDAEYAXwB3AHcAXwB0ACwAIABFAEYAXwB3AHcALAAgAEYAXwByAGUAbQBvAHYAZQBkACwAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQALAAgAEUARgBfAHMAbAB1AGQAZwBlACwAIABRAF8AYwBhAHAALAAgAFEAXwBmAGwAYQByAGUAZAAsACAAUQBfAG8AdQB0ACwAIABFAEMAXwBmAGwAYQByAGUAZAAsACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQALABcAG4AIAAgACAAIAAoADEALwAxADAAMAAwACkAIAAqACAAKAAoAFcAXwB0ACAAKgAgACgAQwBPAEQAXwBpAG4AIAAqACAAKAAxACAALQAgAEYAXwBzAGwAdQBkAGcAZQApACAALQAgAEMATwBEAF8AbwB1AHQAKQAgACoAIABDAEYAXwB3AHcAXwB0ACAAKgAgAEUARgBfAHcAdwApACAAKwAgACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoAEYAXwBzAGwAdQBkAGcAZQAgAC0AIABGAF8AcgBlAG0AbwB2AGUAZAApACkAIAAqACAAQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAKgAgAEUARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAKAA2AC4ANwA4ADQAIAAqACAAMQAwAF4ALQA0ACAAKgAgACgAUQBfAGMAYQBwACAAKwAgAFEAXwBmAGwAYQByAGUAZAAgACsAIABRAF8AbwB1AHQAKQApACAAKwAgACgAUQBfAGYAbABhAHIAZQBkACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQAQwBIADQAKQApACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAB7AFwAXABsAGUAZgB0AHsAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAB9AC0AXABcAGwAZQBmAHQAewA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsAIABRAF8AewBjAGEAcAB9ACsAUQBfAHsAZgBsAGEAcgBlAGQAfQArAFEAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQArAFwAXABsAGUAZgB0AHsAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAEUAQwBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAEMASAA0AH0AXABcAHIAaQBnAGgAdABdAFwAXAByAGkAZwBoAHQAfQBcAFwAcgBpAGcAaAB0AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBfAHQAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABlAGQAIABhAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAGkAbgBcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAaQBuAGwAZQB0ACAAQwBoAGUAbQBpAGMAYQBsACAATwB4AHkAZwBlAG4AIABEAGUAbQBhAG4AZAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAEQAXwBvAHUAdABcACIALAAgAFwAIgBhAHYAZQByAGEAZwBlACAAbwB1AHQAbABlAHQAIABDAE8ARAAgAGMAbwBuAGMAZQBuAHQAcgBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwBEAC8AbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AdwB3AF8AdABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHcAdwBcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwByAGUAbQBvAHYAZQBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAGEAbgBkACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAZQBsAHMAZQB3AGgAZQByAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAF8AcwBsAHUAZABnAGUAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHMAbAB1AGQAZwBlAFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAawBnACAAQwBIADQALwBrAGcAIABDAE8ARABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBjAGEAcABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAYgB5ACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBvAHUAdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAG8AdQB0ACAAbwBmACAAdABoAGUAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIALAAgAFwAIgBtADMAIABDAEgANABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBHAEoALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAGwAYQByAGUAZABDAEgANABcACIALAAgAFwAIgBtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXAAiACwAIABcACIAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdABzACAAbwBmACAARQBGAF8AdwB3ACwAIABFAEYAXwBTAGwAdQBkAGcAZQAgAGEAbgBkACAARQBGAF8AZgBsAGEAcgBlAGQAIABmAHIAbwBtACAAQwBPADIAZQAgAHQAbwAgAEMASAA0ACAAdABvACAAbQBhAHQAYwBoACAAZABhAHQAYQAgAGkAbgAgAFQAYQBiAGwAZQAgAFwAIgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AVABhAGIAbABlACAAQQAuADQALgAxAC4AMwA6ACAATQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHcAdwAsAHQAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAEYAdwB3ACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHcAdwAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgA0ADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgAQwBGAHMAbAB1AGQAZwBlACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEMARgBzAGwAdQBkAGcAZQAsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAG4AbQBhAG4AYQBnAGUAZAAgAGEAZQByAG8AYgBpAGMAIAB0AHIAZQBhAHQAbQBlAG4AdABcACIALAAgADAALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABvAHIALwByAGUAYQBjAHQAbwByAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAYQBsAGwAbwB3ACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAZCIgADIAIABtACkAXAAiACwAIAAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABcAHUAMAAwADMAZQAgADIAbQApAFwAIgAsACAAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAdwB3AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAAQwBIADQAIAAvACAAawBnACAAQwBPAEQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoACAAMAAuADIANQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBzAGwAdQBkAGcAZQBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEMAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBHAEoAIAAvACAAbQAzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAzADcANwApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABDAEgANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0AHMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMAAuADIAMgA4ADkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAEYAZgBsAGEAcgBlAGQALABOADIATwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAawBnACAATgAyAE8AIAAvACAARwBKAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAMQAuADEAMwAyAGUALQA0ACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADMALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAXABuAEUAXwBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABtADMAIABvAHIAIABHAEoAKQBcAG4ARQBGAF8AZgBsAGEAcgBlAGQAXwBOADIATwAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAbABhAHIAZQBkACAAYgBpAG8AZwBhAHMAIAAoAGsAZwAgAE4AMgBPAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZgBsAGEAcgBlAGQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABOADIATwAsAFwAbgAgACAAIAAgACgAUQBfAGYAbABhAHIAZQBkACAALwAgADEAMAAwADAAKQAgACoAIAAoAEUAQwBfAGYAbABhAHIAZQBkACAAKgAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADEALgAzAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAGYAcgBhAGMAewBRAF8AewBmAGwAYQByAGUAZAB9AH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwAgAFwAXABsAGUAZgB0AFsARQBDAF8AewBmAGwAYQByAGUAZAB9ACAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAZgBsAGEAcgBlAGQALABOADIATwB9AFwAXAByAGkAZwBoAHQAXQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAdgBvAGwAdQBtAGUAIABvAGYAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcACIALAAgAFwAIgBrAGcAIABOADIATwAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -13987,15 +14019,15 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14012,12 +14044,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/11_Wastewater_WIP_v02.prename.bak.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BC3BEA-54C2-4A1C-B350-56320BDBAC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D28C02-C589-4333-8214-C48874D0C482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="11.1.1-2 Wastewater CH4" sheetId="69" r:id="rId5"/>
     <sheet name="11.1.3-4 Wastewater N2O" sheetId="120" r:id="rId6"/>
     <sheet name="Constants - Wastewater" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="125" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="126" r:id="rId8"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
@@ -40,7 +40,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -56,9 +66,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -5344,7 +5373,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{60FD3DEC-6132-42B3-A699-403587965D5D}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{30B60E8B-CF5F-4DAE-BCDB-F2A1EE3902D4}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5352,16 +5381,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BA6726C5-D9D8-4D31-81EC-1DC25061E31A}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{90427594-503D-46C3-AB0E-EBAAE18DBC07}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3048A7D2-7F93-4BD0-9D8D-67272EA18191}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{DD709DDE-7A16-4D1B-A356-E4A8AD31BEB5}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{92686BF3-D26B-4679-A40A-852EA84EF852}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{901EE353-B9CC-4C04-BA8B-306FD712CC1D}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{80BA2E2F-6FE0-47D7-9D6D-BFE5E2A9803C}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{5935EE2D-D2AB-47CE-806C-9EB07FC38932}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5370,16 +5399,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{44509B1C-FA74-4B9E-8E16-B7B10FA0ECC6}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{DF105729-3E39-4AD8-A1C1-FFF9E6BDD1EA}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{13EB0E21-1496-43EC-A6FE-FD07ED44F742}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{A7AC1CAA-0CF4-464B-B04D-D4A1734AA79F}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8AAA12F3-3158-4160-9D90-F1610DF90862}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{ECB7544D-C9E1-4956-ABC5-A874DA67C2CA}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5388,16 +5417,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{09B1D7CC-650C-4C00-B0D6-0FD99E350EB9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EAB15B42-28CA-436A-B2E1-12F726403BE8}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F52A7569-0DA7-402F-9AB1-034B445EB227}" name="Data source">
+    <tableColumn id="1" xr3:uid="{99CC1C46-3110-4B86-8A2D-022E73E705B0}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5FD42A51-4C3A-4D1E-A42B-5DA4BF5DCFE0}" name="Data score">
+    <tableColumn id="2" xr3:uid="{A0D120A0-B70D-4125-BC1B-8B20D63A1054}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5406,16 +5435,16 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{DB760DD5-0237-49A8-A230-B47BB1156DE6}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{38AF704B-4AC3-46CB-A2A9-FF80BB25B182}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8881F848-5C9D-4A93-8F3E-9FE78E12D9D8}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{7344BE3D-933D-4CB3-A45F-590BC64BEBC5}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{52CFFC82-08BD-4302-B2DD-3522C2AD5970}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{EE6B8775-F9D7-4607-B873-513E134FDCF0}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5424,7 +5453,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{A7E72203-13BC-4CF7-8169-9096D04EF218}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{E67F4564-FCE8-4E50-8A78-690EEFB29123}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5433,19 +5462,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F8821A07-CBB8-4D58-99FC-46F9AD9B5D06}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{CE9935F7-45FB-40D6-9D83-25C3ADAA29D0}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{808B110B-F4D1-4235-BBE7-A5087AB78BB7}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{6648B445-2608-4B96-B95D-ED7A6BDF511B}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{40B5F840-D9A5-424C-83F4-4BDB382EFDB0}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{A20581E3-80D8-432A-B86C-77BEC72238B0}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4958BC5B-064E-4A15-857F-352B01797ABD}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{C986E6B2-6D07-459B-B746-06DDD77808F7}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A5274952-A1AF-48A5-B96E-D6095F4217A2}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{A5484963-E8AB-4BEF-A6F6-962A9DC60012}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5454,16 +5483,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{1603577B-1419-4AE9-B52C-CD309767E134}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{572A0586-435A-45D0-83CB-D2BBF90C6E04}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{20911576-3EF0-4E1B-A889-87C3CAF4193A}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{FDF9B481-56AD-4DF5-AFA6-955663F8AF74}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A8928862-0C55-4701-8E46-0460079190AF}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B0EE415B-23CE-4DF2-ADD9-9FBC3FC52732}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5472,16 +5501,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{DC5AB438-CBE2-4FFD-BDA9-A83CADD87D88}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{9E899750-2345-47FA-BD87-D8F9DB9C9CBA}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D234EE0E-8F92-4312-BE63-502F946046A1}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{18044A18-7319-4FD1-AACA-5EFA80876994}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7E21E7A6-BB56-4CBA-A22A-56D6354C8C0E}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F7B155E3-4636-47F1-A20F-2B14DF6884E7}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5490,16 +5519,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{D3C26136-7D0C-4262-9DD3-BEB3843BEDE5}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{E21A8B5F-F308-4250-8466-ABE122DD0628}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4CBF8390-5415-4AD3-9812-F085B12FA77F}" name="Month">
+    <tableColumn id="1" xr3:uid="{9228FD07-A52F-4D33-A2DF-0C325123202D}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{12C3240D-243B-47E8-86C5-1020AD6AFF31}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0976F477-2DC8-4431-A2B4-464A51E28CAF}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5508,7 +5537,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{81F10B7B-DBB5-42D3-8E22-E1B4096BF026}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{25BE01B8-AE74-4090-93C0-9F2585B2753F}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5528,52 +5557,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D9579F68-9384-4395-9B40-A666F880BDDB}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{0B4692EE-3DA5-4F33-B8ED-1FD4F634B1E7}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B5C3A31B-2242-46CB-B0BD-99DE0082E553}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DB9D8CBF-CE36-46FF-ADB6-68DAC58EDE1E}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B4374E36-14BC-476E-901E-FAF15F4C4C67}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{2E64B7B3-8C67-4E80-914C-D2818F2B3052}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6EFD5B4A-1034-4FCF-8049-14B5F75E9A5F}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{28D644A1-08C2-477B-9E8B-95E5591F7944}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2F2DF928-E0E4-4BDB-8FF2-39BADE8602B4}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{29650014-14B9-4204-B028-9A1ABE36DD86}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A408F48C-E01F-4C66-B671-371CEDB14FA8}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{FF41A470-F597-4163-A7C5-54DCC7DDC808}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EA17D570-9828-4407-9280-37420A993AAB}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{5AE4961A-8823-43D9-95C5-E28C501B698C}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8F2C9E0D-DA9D-429C-82B7-E2683EF71F6F}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{F817CC10-DA85-482F-986E-3A29A653AF0B}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{08E56A3F-15A4-4F37-BAE2-6B57DDFE2992}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{1B48A10A-17CB-4D2F-A0E4-A8599D40A469}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A3C2F1A6-E172-41C6-8C78-5E47C0C5C747}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{E816252C-1145-4B1A-8BC2-06E2E9ACA81C}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6F45BD40-E4D6-4DCC-87FC-414A1FBEFEA6}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{407B1FD0-ACAF-4A77-8EB3-B45AC2848E88}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{17DA757C-6CDA-4C52-B8B6-420D5941EF6C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{FDE08AD2-D6C4-458F-B064-FFD0AC4FF7C7}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5268FDA8-7DF2-4A8C-AACF-EF2AB5BC2B49}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{DEAF6568-8962-4FC6-B6A5-3600F17747B4}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{B004BF9B-155B-4440-A60F-7DFCC41D53AD}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{603F818F-3F8E-4B6B-8474-19EB2D4B2078}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{8ABF53AC-2C64-414A-977B-8E8C687200DB}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{9628CF82-B2D0-4FF8-9962-6A0F2F6CA7F7}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{165C0C41-E29C-484F-9F19-554BFA51EA9B}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{770C2488-4416-4427-8990-A550DA980D9C}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5582,16 +5611,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{782546F2-95EA-4798-BEF5-E9A9FD9348A7}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{E3C18E34-15E8-4C47-8C8C-FAA56730FC4D}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AA931D7D-C70B-44B6-A950-2C74FE01DBD7}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{E4226D57-5B9C-45FE-931A-B024FA2BA7BB}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B414394C-46C8-4708-A016-96AB55B2CB24}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5EC2D26E-B5C8-4C0E-8E88-9AAC02CC84C4}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5618,20 +5647,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE2901E4-74D4-491C-9839-A10E08538903}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D27EA4B7-E5E1-4C29-BD1A-04D0F1CDB93F}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{13A7A6A1-7645-4FB3-95BA-39FF4C7FE645}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{94DF1764-C1F4-4325-ACBB-ADDBDE8C0154}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{417988F4-ED4B-45FF-A91E-9D85E753F6E4}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{776768E7-66C4-446B-BCFD-88FA26CE3EE7}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B962FF60-EEFE-4021-AD77-4E3462E1AF13}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{FB11E370-54BC-4CE6-BCF9-C473C7E368BC}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5640,12 +5669,12 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2813C8E6-E9CE-4977-8FB4-47FB574DC02B}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{824F900F-505D-492F-AA6E-D2D7E7CD1122}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{ABC00590-0BDD-4727-A087-CF9BFD527FC6}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{5B6B81FD-62C4-4FDE-9C33-7791C470F745}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5654,16 +5683,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE88C359-14EF-4A97-A2E4-175687F0066C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{8E647256-1EF4-4A7C-9FCF-CE16EBA69288}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E9620700-E2AA-43F7-823B-1D93E54A99A9}" name="Gas">
+    <tableColumn id="1" xr3:uid="{238FBC0C-2AF2-4DF7-B7F9-B7F57CE21B65}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9A583022-0F51-47E6-9CF0-DCE0148B9061}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{2BE46C13-5756-4CE3-8752-64D01A57B987}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5672,7 +5701,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8E394016-4C3B-4484-A0FF-3CFB83C5E43D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{8E35B393-BB5E-4A46-A1F0-24D0A2C74FFA}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5681,19 +5710,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D7EC98A6-A45F-4EEE-9F93-E4FB3D0A7D7D}" name="Gas">
+    <tableColumn id="1" xr3:uid="{DF50644C-6FAB-4C39-89AD-3A9D796DB0F2}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{73EF9163-4C06-47F3-8994-067EFD7F0FE5}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{3F435C04-50E3-4080-BF7F-1A05FD179A4C}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE75DEEB-09D7-4CFF-885C-AF9F1D49BD34}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{1CF6A86A-70F1-4B1F-ACEB-875B5C7443E2}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{213C32CE-1368-48BB-87AB-0D2F801910D0}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{B73ED961-417F-4010-80F2-6FF70FB03699}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FF28DF7C-D3F6-4240-9ED5-975D79231313}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{150A75F1-79C6-4E1E-BE92-48B7537AB5F0}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5702,7 +5731,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{2678E15E-9743-4D6B-B08F-54FA1F7BD4E6}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{DAFBA8DD-508D-4EFA-8F91-761FA308D532}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5722,52 +5751,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{258A2775-12F7-4B6E-B50C-2B734CED6764}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{B95F8E12-8C17-4F04-91E8-5E552B19D3E0}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CA57A8D6-0E1B-4395-8BBD-8EB2909C6375}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{2320BD6A-E1E4-48DD-B5E8-6DADE40E7D27}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{640685BD-3D0B-4B49-994F-2049CD844190}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{C005F782-72AE-4702-9807-A686FB0959C2}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B41BB388-73CC-4E31-9702-0644757B771D}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{3C58AD4D-71CF-499A-BDF6-86314B3F9671}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F65571A7-99C4-419A-ACC9-DB99F6270790}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{5C309C87-2F75-4688-A6E1-258E9FCFBD05}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{1A2EB41B-4703-47CB-A6BA-B23ECFDE75DC}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{BBF78E3F-3584-4790-9E30-55766C340EEC}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D4FCC700-6BCB-42F6-A269-73CB179D12DE}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{1E71169A-70C9-414C-AD7F-A49554234675}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0B04A76E-8B93-43EF-9F74-AAE65AEC4441}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{3C8CEFD1-B782-4250-8A9E-2B07C2AAA377}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{13D3D99C-422D-4DB4-BAFE-4D5F232E4C8B}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{6A9650F7-6E29-4690-8BB6-90163E2994B6}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{23F7ECD7-4755-4ED3-8B32-64F398DDA30D}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{8C231AEF-A038-49D4-A973-F71F4D438211}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{358C427E-C96B-4053-A990-1B2058EBFC64}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{C9801D74-DC47-4340-8F31-8447FD7F6A29}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{3130F307-B98C-4067-B80F-2542F94A1BE0}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{0BCCB7D9-AD8B-4C36-8C07-7570920F98E7}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8D192874-9822-4C4F-9A9E-B334BAC2FFB8}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{234FF138-B27C-4B62-8F9B-C37CA7CAC2D3}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{A79D36E5-993C-4167-BDE8-6407717CAB24}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{707DE610-55E7-4C2B-A655-DC3A68E07726}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{A4876D80-2BA9-4B93-A438-B39231AC151A}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{4C8B938B-15ED-44B7-AE5F-0B97F397EB93}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C13F21D8-24C0-4A6E-8DE5-7781BD4EA367}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{CAADAB65-A513-48D5-B5A0-48D595DDC14D}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5776,16 +5805,16 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{ABD9088D-21E6-4B13-B698-A88D317D61B7}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{C40E40B1-1238-404E-90D4-5CBA6C401B63}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{42339138-CF75-47CE-98E2-00C999CD6CD9}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{75FFA69A-9E31-49AE-91B6-95A172025521}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53AA9C04-0F8D-43AC-AB39-360AF88BE8CC}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{5BEF6136-8996-4E40-8803-A96D1FA83D99}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5794,7 +5823,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F0282294-800C-4FCE-87FB-E5433DFD7DD5}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{9AD0C5A9-EF00-4938-A16D-3C51E0439BA7}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5802,16 +5831,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{EB6FF107-1CC5-47A6-BFC2-A373ED5BA9DC}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{195B97CC-65C4-4301-9D48-458254FAEBF3}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{81FB7AAB-B954-4F7F-880E-D1D6DDF943A7}" name="MAT">
+    <tableColumn id="2" xr3:uid="{974E4BFA-1A60-4BA9-B2E0-13EC0ED4C626}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F72C74A5-51F2-4215-9ABA-7C66657A62EE}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{7B2070AF-B02C-49F1-AF64-8F307DA73013}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6AA30C8F-73A6-4FD1-B809-BD18E5A99F76}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{F5855D94-A891-4C9E-AE30-49A2128B61E3}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9790,7 +9819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9990F8D9-C280-49C7-B33D-9DB18A15652B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78DA856-38CA-4516-B7C9-CA0CA010ED6F}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13782,15 +13811,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -13801,11 +13821,11 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQA6ACAAVwBhAHMAdABlAHcAYQB0AGUAcgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAxAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABvAG4AcwBpAHQAZQAgAFcAYQBzAHQAZQB3AGEAdABlAHIAIABNAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABcAGYAcgBhAGMAewAxAH0AewAxADAAMAAwAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdABbAFwAXABsAGUAZgB0ACgAVwBfAHQAXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoAEMATwBEAF8AewBpAG4AfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AHMAbAB1AGQAZwBlAH0AKQAtAEMATwBEAF8AewBvAHUAdAB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAQwBGAF8AewB3AHcALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAdwB3AH0AXABcAHIAaQBnAGgAdAApACsAXABcAGwAZQBmAHQAKABXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKABGAF8AewBzAGwAdQBkAGcAZQB9AC0ARgBfAHsAcgBlAG0AbwB2AGUAZAB9ACkAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHMAbAB1AGQAZwBlACwAdAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHMAbAB1AGQAZwBlAH0AXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKAA2AC4ANwA4ADQAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQA0AH0AXABcAHQAaQBtAGUAcwAoAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQApAFwAXAByAGkAZwBoAHQAKQArAFwAXABsAGUAZgB0ACgAUQBfAHsAZgBsAGEAcgBlAGQAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHIAaQBnAGgAdABdAFwAbgBXAF8AdAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAKABtADMAKQBcAG4AQwBPAEQAXwBpAG4AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGkAbgBsAGUAdAAgAEMAaABlAG0AaQBjAGEAbAAgAE8AeAB5AGcAZQBuACAARABlAG0AYQBuAGQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4ARgBfAHMAbAB1AGQAZwBlACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAEMATwBEACAAcgBlAG0AbwB2AGUAZAAgAGYAcgBvAG0AIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAYQBzACAAcwBsAHUAZABnAGUAXABuAEMATwBEAF8AbwB1AHQAIAA9ACAAYQB2AGUAcgBhAGcAZQAgAG8AdQB0AGwAZQB0ACAAQwBPAEQAIABjAG8AbgBjAGUAbgB0AHIAYQB0AGkAbwBuACAAbwBmACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgACgAawBnACAAQwBPAEQALwBtADMAKQBcAG4AQwBGAF8AdwB3AF8AdAAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdAAgAHUAcwBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAIAB3AGEAcwB0AGUAdwBhAHQAZQByAFwAbgBFAEYAXwB3AHcAIAA9ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4ARgBfAHIAZQBtAG8AdgBlAGQAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcAG4AQwBGAF8AcwBsAHUAZABnAGUAXwB0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHMAbAB1AGQAZwBlAFwAbgBFAEYAXwBzAGwAdQBkAGcAZQAgAD0AIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAKABrAGcAIABDAE8AMgBlAC8AawBnACAAQwBPAEQAKQBcAG4AUQBfAGMAYQBwACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtADMAIABDAEgANAApAFwAbgBRAF8AZgBsAGEAcgBlAGQAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZAAgACgAbQAzACAAQwBIADQAKQBcAG4AUQBfAG8AdQB0ACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAKABtADMAIABDAEgANAApAFwAbgBFAEMAXwBmAGwAYQByAGUAZAAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAEcASgAvAG0AMwApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAEMASAA0ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkACAAKABrAGcAIABDAE8AMgBlAC8ARwBKACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAHQALAAgAEMATwBEAF8AaQBuACwAIABGAF8AcwBsAHUAZABnAGUALAAgAEMATwBEAF8AbwB1AHQALAAgAEMARgBfAHcAdwBfAHQALAAgAEUARgBfAHcAdwAsACAARgBfAHIAZQBtAG8AdgBlAGQALAAgAEMARgBfAHMAbAB1AGQAZwBlAF8AdAAsACAARQBGAF8AcwBsAHUAZABnAGUALAAgAFEAXwBjAGEAcAAsACAAUQBfAGYAbABhAHIAZQBkACwAIABRAF8AbwB1AHQALAAgAEUAQwBfAGYAbABhAHIAZQBkACwAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAAsAFwAbgAgACAAIAAgACgAMQAvADEAMAAwADAAKQAgACoAIAAoACgAVwBfAHQAIAAqACAAKABDAE8ARABfAGkAbgAgACoAIAAoADEAIAAtACAARgBfAHMAbAB1AGQAZwBlACkAIAAtACAAQwBPAEQAXwBvAHUAdAApACAAKgAgAEMARgBfAHcAdwBfAHQAIAAqACAARQBGAF8AdwB3ACkAIAArACAAKABXAF8AdAAgACoAIAAoAEMATwBEAF8AaQBuACAAKgAgACgARgBfAHMAbAB1AGQAZwBlACAALQAgAEYAXwByAGUAbQBvAHYAZQBkACkAKQAgACoAIABDAEYAXwBzAGwAdQBkAGcAZQBfAHQAIAAqACAARQBGAF8AcwBsAHUAZABnAGUAKQAgAC0AIAAoADYALgA3ADgANAAgACoAIAAxADAAXgAtADQAIAAqACAAKABRAF8AYwBhAHAAIAArACAAUQBfAGYAbABhAHIAZQBkACAAKwAgAFEAXwBvAHUAdAApACkAIAArACAAKABRAF8AZgBsAGEAcgBlAGQAIAAqACAAKABFAEMAXwBmAGwAYQByAGUAZAAgACoAIABFAEYAXwBmAGwAYQByAGUAZABDAEgANAApACkAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAE0AZQBhAHMAdQByAGUAbQBlAG4AdAAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAZgByAGEAYwB7ADEAfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AHsAXABcAGwAZQBmAHQAewBXAF8AdABcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0AFsAQwBPAEQAXwB7AGkAbgB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARgBfAHsAcwBsAHUAZABnAGUAfQApAC0AQwBPAEQAXwB7AG8AdQB0AH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABDAEYAXwB7AHcAdwAsAHQAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB3AHcAfQBcAFwAcgBpAGcAaAB0AH0AKwBcAFwAbABlAGYAdAB7AFcAXwB0AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAWwBDAE8ARABfAHsAaQBuAH0AXABcAHQAaQBtAGUAcwAoAEYAXwB7AHMAbAB1AGQAZwBlAH0ALQBGAF8AewByAGUAbQBvAHYAZQBkAH0AKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEMARgBfAHsAcwBsAHUAZABnAGUALAB0AH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcwBsAHUAZABnAGUAfQBcAFwAcgBpAGcAaAB0AH0ALQBcAFwAbABlAGYAdAB7ADYALgA3ADgANABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADQAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwAgAFEAXwB7AGMAYQBwAH0AKwBRAF8AewBmAGwAYQByAGUAZAB9ACsAUQBfAHsAbwB1AHQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9ACsAXABcAGwAZQBmAHQAewBRAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABcAFwAbABlAGYAdABbACAARQBDAF8AewBmAGwAYQByAGUAZAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGYAbABhAHIAZQBkACwAQwBIADQAfQBcAFwAcgBpAGcAaAB0AF0AXABcAHIAaQBnAGgAdAB9AFwAXAByAGkAZwBoAHQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AdABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIAB3AGEAcwB0AGUAdwBhAHQAZQByACAAdAByAGUAYQB0AGUAZAAgAGEAdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBEAF8AaQBuAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABpAG4AbABlAHQAIABDAGgAZQBtAGkAYwBhAGwAIABPAHgAeQBnAGUAbgAgAEQAZQBtAGEAbgBkACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIABhAHMAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8ARABfAG8AdQB0AFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABvAHUAdABsAGUAdAAgAEMATwBEACAAYwBvAG4AYwBlAG4AdAByAGEAdABpAG8AbgAgAG8AZgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAawBnACAAQwBPAEQALwBtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwB3AHcAXwB0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AdwB3AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAHIAZQBtAG8AdgBlAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAQwBPAEQAIAByAGUAbQBvAHYAZQBkACAAZgByAG8AbQAgAHQAaABlACAAdwBhAHMAdABlAHcAYQB0AGUAcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAYQBuAGQAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIABlAGwAcwBlAHcAaABlAHIAZQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAXwBzAGwAdQBkAGcAZQBfAHQAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwByAHIAZQBjAHQAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcwBsAHUAZABnAGUAXAAiACwAIABcACIAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAGwAdQBkAGcAZQBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGsAZwAgAEMATwBEAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGMAYQBwAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIABiAHkAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG8AdQB0AFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAbwB1AHQAIABvAGYAIAB0AGgAZQAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5AFwAIgAsACAAXAAiAG0AMwAgAEMASAA0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAbABhAHIAZQBkAEMASAA0AFwAIgAsACAAXAAiAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdABcACIALAAgAFwAIgB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEMAaABhAG4AZwBlAGQAIAB1AG4AaQB0AHMAIABvAGYAIABFAEYAXwB3AHcALAAgAEUARgBfAFMAbAB1AGQAZwBlACAAYQBuAGQAIABFAEYAXwBmAGwAYQByAGUAZAAgAGYAcgBvAG0AIABDAE8AMgBlACAAdABvACAAQwBIADQAIAB0AG8AIABtAGEAdABjAGgAIABkAGEAdABhACAAaQBuACAAVABhAGIAbABlACAAXAAiACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIABBAC4ANAAuADEALgAzADoAIABNAGUAdABoAGEAbgBlACAAYwBvAHIAcgBlAGMAdABpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQAgAHQAeQBwAGUAIAB0ACAAdQBzAGUAZAAgAHQAbwAgAHQAcgBlAGEAdAAgAHcAYQBzAHQAZQB3AGEAdABlAHIAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAdwB3ACwAdAApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAdwBhAHMAdABlAHcAYQB0AGUAcgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMARgB3AHcALAB0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4AMwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAYwBpAGwAaQB0AHkAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBDAEYAdwB3ACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFQAYQBiAGwAZQAgAEEALgA0AC4AMQAuADQAOgAgAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABDAEYAcwBsAHUAZABnAGUALAB0ACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AcgByAGUAYwB0AGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAZgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAIAB1AHMAZQBkACAAdABvACAAdAByAGUAYQB0ACAAcwBsAHUAZABnAGUAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBVAG4AaQB0AFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAxAC4ANABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBhAGMAaQBsAGkAdAB5ACAAdAB5AHAAZQAgAHQAXAAiACwAIABcACIAQwBGAHMAbAB1AGQAZwBlACwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBtAGEAbgBhAGcAZQBkACAAYQBlAHIAbwBiAGkAYwAgAHQAcgBlAGEAdABtAGUAbgB0AFwAIgAsACAAMAAuADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AG8AcgAvAHIAZQBhAGMAdABvAHIAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaABhAGwAbABvAHcAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABkIiAAMgAgAG0AKQBcACIALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAFwAdQAwADAAMwBlACAAMgBtACkAXAAiACwAIAAwAC4AOABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQBzAHQAZQB3AGEAdABlAHIAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgB3AHcAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABrAGcAIABDAE8ARABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAIAAwAC4AMgA1ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBGAHMAbAB1AGQAZwBlAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGsAZwAgAEMATwBEAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAyADUAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAQwBmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEcASgAgAC8AIABtADMAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoADAALgAwADMANwA3ACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAbAB1AGQAZwBlACAAYgBpAG8AZwBhAHMAIABmAGwAYQByAGUAZABcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAEMASAA0AFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdABcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAEcASgBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAcwBcACIAKQApADsAXABuAFwAbgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAyADgAOQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAGYAbABhAHIAZQBkAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUARgBmAGwAYQByAGUAZAAsAE4AMgBPAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFUAbgBpAHQAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBrAGcAIABOADIATwAgAC8AIABHAEoAXAAiACkAKQA7AFwAbgBcAG4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADEALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdABzAFwAIgApACkAOwBcAG4AXABuAFcAYQBzAHQAZQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKAAxAC4AMQAzADIAZQAtADQAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxADoAIABXAGEAcwB0AGUAdwBhAHQAZQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADEALgAxAC4AMwAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AbgBzAGkAdABlACAAVwBhAHMAdABlAHcAYQB0AGUAcgAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwBcAG4ARQBfAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABuAFEAXwBmAGwAYQByAGUAZAAgAD0AIAB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAIAAoAG0AMwAgAG8AcgAgAEcASgApAFwAbgBFAEYAXwBmAGwAYQByAGUAZABfAE4AMgBPACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBsAGEAcgBlAGQAIABiAGkAbwBnAGEAcwAgACgAawBnACAATgAyAE8ALwBHAEoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBmAGwAYQByAGUAZAAsACAARQBDAF8AZgBsAGEAcgBlAGQALAAgAEUARgBfAGYAbABhAHIAZQBkAE4AMgBPACwAXABuACAAIAAgACAAKABRAF8AZgBsAGEAcgBlAGQAIAAvACAAMQAwADAAMAApACAAKgAgACgARQBDAF8AZgBsAGEAcgBlAGQAIAAqACAARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8ATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQAxAC4AMQAuADMALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAZgByAGEAYwB7AFEAXwB7AGYAbABhAHIAZQBkAH0AfQB7ADEAMAAwADAAfQBcAFwAdABpAG0AZQBzACAAXABcAGwAZQBmAHQAWwBFAEMAXwB7AGYAbABhAHIAZQBkAH0AIABcAFwAdABpAG0AZQBzACAARQBGAF8AewBmAGwAYQByAGUAZAAsAE4AMgBPAH0AXABcAHIAaQBnAGgAdABdAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBmAGwAYQByAGUAZABcACIALAAgAFwAIgB2AG8AbAB1AG0AZQAgAG8AZgAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AZgBsAGEAcgBlAGQAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABvAGYAIABzAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAZgBsAGEAcgBlAGQAXAAiACwAIABcACIARwBKAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBsAGEAcgBlAGQATgAyAE8AXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGwAYQByAGUAZAAgAGIAaQBvAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAE4AMgBPAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBNAGUAdABoAGEAbgBlAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVwBhAHMAdABlAHcAYQB0AGUAcgBUAHIAZQBhAHQAbQBlAG4AdABfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE0AZQB0AGgAYQBuAGUAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBXAGEAcwB0AGUAdwBhAHQAZQByAFQAcgBlAGEAdABtAGUAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATQBlAHQAaABhAG4AZQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFcAYQBzAHQAZQB3AGEAdABlAHIAVAByAGUAYQB0AG0AZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBDAG8AcgByAGUAYwB0AGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUAQwBvAHIAcgBlAGMAdABpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEMAbwByAHIAZQBjAHQAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ARABhAHQAYQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAF8AVABpAHQAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBfAFMAbwB1AHIAYwBlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFQAaQB0AGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AVQBuAGkAdAAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFcAYQBzAHQAZQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBTAGwAdQBkAGcAZQBCAGkAbwBnAGEAcwBGAGwAYQByAGUAZABfAEQAYQB0AGEAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBVAG4AaQB0ACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AVwBhAHMAdABlAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAFMAbAB1AGQAZwBlAEIAaQBvAGcAYQBzAEYAbABhAHIAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBXAGEAcwB0AGUAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAUwBsAHUAZABnAGUAQgBpAG8AZwBhAHMARgBsAGEAcgBlAGQAXwBEAGEAdABhACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBUAGkAdABsAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFcAYQBzAHQAZQB3AGEAdABlAHIAXwBOADIATwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AMQBfADMAXwAxAF8AXwAxAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAGwAYQByAGUAZABCAGkAbwBnAGEAcwBfAFUAbgBpAHQAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAVwBhAHMAdABlAHcAYQB0AGUAcgBfAE4AMgBPAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwAxAF8AMwBfADEAXwBfADEAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAbABhAHIAZQBkAEIAaQBvAGcAYQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBXAGEAcwB0AGUAdwBhAHQAZQByAF8ATgAyAE8AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADEAXwAzAF8AMQBfAF8AMQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgBsAGEAcgBlAGQAQgBpAG8AZwBhAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -14000,15 +14020,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -14019,7 +14040,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
@@ -14027,7 +14048,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14044,4 +14065,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>